--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_124_R13.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_124_R13.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.3077</v>
+        <v>7.4097</v>
       </c>
       <c r="E2" t="n">
-        <v>4.4732</v>
+        <v>5.3736</v>
       </c>
       <c r="F2" t="n">
-        <v>1.8345</v>
+        <v>2.0361</v>
       </c>
       <c r="G2" t="n">
         <v>5.0907</v>
@@ -610,13 +610,13 @@
         <v>1.8556</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.1747</v>
+        <v>-0.0727</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.4244</v>
+        <v>0.476</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.7503</v>
+        <v>-0.5487</v>
       </c>
       <c r="V2" t="n">
         <v>0.5361</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.7099</v>
+        <v>4.5612</v>
       </c>
       <c r="E3" t="n">
-        <v>4.5762</v>
+        <v>3.1921</v>
       </c>
       <c r="F3" t="n">
-        <v>1.1338</v>
+        <v>1.369</v>
       </c>
       <c r="G3" t="n">
         <v>0.1469</v>
@@ -688,13 +688,13 @@
         <v>2.0876</v>
       </c>
       <c r="S3" t="n">
-        <v>2.0089</v>
+        <v>0.8601</v>
       </c>
       <c r="T3" t="n">
-        <v>2.6384</v>
+        <v>1.2544</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.6294999999999999</v>
+        <v>-0.3943</v>
       </c>
       <c r="V3" t="n">
         <v>1.4665</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.7794</v>
+        <v>4.4152</v>
       </c>
       <c r="E4" t="n">
-        <v>1.6984</v>
+        <v>1.0654</v>
       </c>
       <c r="F4" t="n">
-        <v>3.081</v>
+        <v>3.3498</v>
       </c>
       <c r="G4" t="n">
         <v>3.6798</v>
@@ -766,13 +766,13 @@
         <v>0.9278</v>
       </c>
       <c r="S4" t="n">
-        <v>0.883</v>
+        <v>0.5188</v>
       </c>
       <c r="T4" t="n">
-        <v>1.0815</v>
+        <v>0.4485</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.1986</v>
+        <v>0.0703</v>
       </c>
       <c r="V4" t="n">
         <v>1.6083</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.0996</v>
+        <v>4.3592</v>
       </c>
       <c r="E5" t="n">
-        <v>1.1003</v>
+        <v>1.7214</v>
       </c>
       <c r="F5" t="n">
-        <v>1.9993</v>
+        <v>2.6378</v>
       </c>
       <c r="G5" t="n">
         <v>3.8253</v>
@@ -844,13 +844,13 @@
         <v>1.1598</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.1742</v>
+        <v>0.0854</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.5737</v>
+        <v>0.0474</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.6005</v>
+        <v>0.038</v>
       </c>
       <c r="V5" t="n">
         <v>1.6083</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>N. REUVERS</t>
+          <t>M. COSTELLO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,40 +877,40 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.8749</v>
+        <v>2.8781</v>
       </c>
       <c r="E6" t="n">
-        <v>0.5397999999999999</v>
+        <v>2.0474</v>
       </c>
       <c r="F6" t="n">
-        <v>2.335</v>
+        <v>0.8307</v>
       </c>
       <c r="G6" t="n">
-        <v>1.1964</v>
+        <v>3.2024</v>
       </c>
       <c r="H6" t="n">
-        <v>1.521</v>
+        <v>0.3951</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.3246</v>
+        <v>2.8074</v>
       </c>
       <c r="J6" t="n">
-        <v>0.8249</v>
+        <v>1.4226</v>
       </c>
       <c r="K6" t="n">
-        <v>1.9326</v>
+        <v>0.1344</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.1077</v>
+        <v>1.2882</v>
       </c>
       <c r="M6" t="n">
-        <v>0.3715</v>
+        <v>1.7798</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.4116</v>
+        <v>0.2606</v>
       </c>
       <c r="O6" t="n">
-        <v>0.7831</v>
+        <v>1.5192</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
@@ -922,28 +922,28 @@
         <v>1.1598</v>
       </c>
       <c r="S6" t="n">
-        <v>0.6062</v>
+        <v>-0.0718</v>
       </c>
       <c r="T6" t="n">
-        <v>0.1968</v>
+        <v>0.4288</v>
       </c>
       <c r="U6" t="n">
-        <v>0.4094</v>
+        <v>-0.5006</v>
       </c>
       <c r="V6" t="n">
-        <v>1.0722</v>
+        <v>-0.2525</v>
       </c>
       <c r="W6" t="n">
-        <v>0.6778999999999999</v>
+        <v>1.3558</v>
       </c>
       <c r="X6" t="n">
-        <v>0.3943</v>
+        <v>-1.6083</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M. COSTELLO</t>
+          <t>N. REUVERS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,40 +955,40 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>2.5743</v>
+        <v>2.872</v>
       </c>
       <c r="E7" t="n">
-        <v>1.5756</v>
+        <v>0.3353</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9987</v>
+        <v>2.5367</v>
       </c>
       <c r="G7" t="n">
-        <v>3.2024</v>
+        <v>1.1964</v>
       </c>
       <c r="H7" t="n">
-        <v>0.3951</v>
+        <v>1.521</v>
       </c>
       <c r="I7" t="n">
-        <v>2.8074</v>
+        <v>-0.3246</v>
       </c>
       <c r="J7" t="n">
-        <v>1.4226</v>
+        <v>0.8249</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1344</v>
+        <v>1.9326</v>
       </c>
       <c r="L7" t="n">
-        <v>1.2882</v>
+        <v>-1.1077</v>
       </c>
       <c r="M7" t="n">
-        <v>1.7798</v>
+        <v>0.3715</v>
       </c>
       <c r="N7" t="n">
-        <v>0.2606</v>
+        <v>-0.4116</v>
       </c>
       <c r="O7" t="n">
-        <v>1.5192</v>
+        <v>0.7831</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
@@ -1000,22 +1000,22 @@
         <v>1.1598</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.3756</v>
+        <v>0.6034</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.0431</v>
+        <v>-0.0077</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.3325</v>
+        <v>0.6111</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.2525</v>
+        <v>1.0722</v>
       </c>
       <c r="W7" t="n">
-        <v>1.3558</v>
+        <v>0.6778999999999999</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.6083</v>
+        <v>0.3943</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.8879</v>
+        <v>2.173</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.1531</v>
+        <v>-0.5319</v>
       </c>
       <c r="F8" t="n">
-        <v>3.041</v>
+        <v>2.705</v>
       </c>
       <c r="G8" t="n">
         <v>1.381</v>
@@ -1078,13 +1078,13 @@
         <v>1.6237</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0431</v>
+        <v>0.3282</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.6563</v>
+        <v>-0.0351</v>
       </c>
       <c r="U8" t="n">
-        <v>0.6994</v>
+        <v>0.3633</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>1.3583</v>
+        <v>0.6587</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.3263</v>
+        <v>-2.7234</v>
       </c>
       <c r="F9" t="n">
-        <v>3.6846</v>
+        <v>3.3821</v>
       </c>
       <c r="G9" t="n">
         <v>-2.218</v>
@@ -1156,13 +1156,13 @@
         <v>2.0876</v>
       </c>
       <c r="S9" t="n">
-        <v>1.4888</v>
+        <v>0.7892</v>
       </c>
       <c r="T9" t="n">
-        <v>1.1641</v>
+        <v>0.767</v>
       </c>
       <c r="U9" t="n">
-        <v>0.3247</v>
+        <v>0.0222</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.3342</v>
+        <v>0.2466</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.3636</v>
+        <v>0.4188</v>
       </c>
       <c r="F10" t="n">
-        <v>0.0294</v>
+        <v>-0.1722</v>
       </c>
       <c r="G10" t="n">
         <v>0.6667999999999999</v>
@@ -1234,13 +1234,13 @@
         <v>1.3917</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.3901</v>
+        <v>0.1907</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.4323</v>
+        <v>0.3501</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0422</v>
+        <v>-0.1595</v>
       </c>
       <c r="V10" t="n">
         <v>-2.0026</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.7976</v>
+        <v>-0.5962</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.4162</v>
+        <v>-0.6771</v>
       </c>
       <c r="F11" t="n">
-        <v>0.6186</v>
+        <v>0.0809</v>
       </c>
       <c r="G11" t="n">
         <v>2.3897</v>
@@ -1312,13 +1312,13 @@
         <v>0.9278</v>
       </c>
       <c r="S11" t="n">
-        <v>0.3488</v>
+        <v>0.5502</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.5895</v>
+        <v>0.1496</v>
       </c>
       <c r="U11" t="n">
-        <v>0.9384</v>
+        <v>0.4007</v>
       </c>
       <c r="V11" t="n">
         <v>-2.1444</v>
@@ -1345,10 +1345,10 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.5849</v>
+        <v>-2.982</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.6765</v>
+        <v>-5.0736</v>
       </c>
       <c r="F12" t="n">
         <v>2.0915</v>
@@ -1390,10 +1390,10 @@
         <v>0.6959</v>
       </c>
       <c r="S12" t="n">
-        <v>1.1756</v>
+        <v>0.7784</v>
       </c>
       <c r="T12" t="n">
-        <v>1.2977</v>
+        <v>0.9006</v>
       </c>
       <c r="U12" t="n">
         <v>-0.1221</v>
@@ -1423,10 +1423,10 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>24.8753</v>
+        <v>25.9955</v>
       </c>
       <c r="E13" t="n">
-        <v>4.0278</v>
+        <v>5.147999999999999</v>
       </c>
       <c r="F13" t="n">
         <v>20.8474</v>
@@ -1468,13 +1468,13 @@
         <v>15.0771</v>
       </c>
       <c r="S13" t="n">
-        <v>3.4398</v>
+        <v>4.559900000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>3.6592</v>
+        <v>4.7796</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.2194</v>
+        <v>-0.2196000000000001</v>
       </c>
       <c r="V13" t="n">
         <v>1.103300000000001</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>O. DA SILVA</t>
+          <t>J. JESSUP</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.6801</v>
+        <v>2.9875</v>
       </c>
       <c r="E14" t="n">
-        <v>0.9974</v>
+        <v>1.0904</v>
       </c>
       <c r="F14" t="n">
-        <v>2.6827</v>
+        <v>1.8971</v>
       </c>
       <c r="G14" t="n">
-        <v>0.1696</v>
+        <v>3.0396</v>
       </c>
       <c r="H14" t="n">
-        <v>0.6915</v>
+        <v>0.3963</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.5219</v>
+        <v>2.6433</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.37</v>
+        <v>2.7934</v>
       </c>
       <c r="K14" t="n">
-        <v>0.306</v>
+        <v>0.6722</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.6758999999999999</v>
+        <v>2.1212</v>
       </c>
       <c r="M14" t="n">
-        <v>0.5396</v>
+        <v>0.2462</v>
       </c>
       <c r="N14" t="n">
-        <v>0.3856</v>
+        <v>-0.2759</v>
       </c>
       <c r="O14" t="n">
-        <v>0.154</v>
+        <v>0.5221</v>
       </c>
       <c r="P14" t="n">
         <v>-0.4639</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.3917</v>
+        <v>-2.3195</v>
       </c>
       <c r="R14" t="n">
-        <v>0.9278</v>
+        <v>1.8556</v>
       </c>
       <c r="S14" t="n">
-        <v>1.3249</v>
+        <v>-0.6605</v>
       </c>
       <c r="T14" t="n">
-        <v>1.6869</v>
+        <v>-0.4558</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.362</v>
+        <v>-0.2047</v>
       </c>
       <c r="V14" t="n">
-        <v>2.6495</v>
+        <v>1.0722</v>
       </c>
       <c r="W14" t="n">
         <v>1.0722</v>
       </c>
       <c r="X14" t="n">
-        <v>1.5773</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>N. GIFFEY</t>
+          <t>O. DA SILVA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.5932</v>
+        <v>2.9331</v>
       </c>
       <c r="E15" t="n">
-        <v>3.3109</v>
+        <v>-0.0641</v>
       </c>
       <c r="F15" t="n">
-        <v>0.2823</v>
+        <v>2.9972</v>
       </c>
       <c r="G15" t="n">
-        <v>1.5373</v>
+        <v>0.1696</v>
       </c>
       <c r="H15" t="n">
-        <v>0.3662</v>
+        <v>0.6915</v>
       </c>
       <c r="I15" t="n">
-        <v>1.1711</v>
+        <v>-0.5219</v>
       </c>
       <c r="J15" t="n">
-        <v>1.6592</v>
+        <v>-0.37</v>
       </c>
       <c r="K15" t="n">
-        <v>0.6421</v>
+        <v>0.306</v>
       </c>
       <c r="L15" t="n">
-        <v>1.0171</v>
+        <v>-0.6758999999999999</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.1219</v>
+        <v>0.5396</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.2759</v>
+        <v>0.3856</v>
       </c>
       <c r="O15" t="n">
         <v>0.154</v>
       </c>
       <c r="P15" t="n">
-        <v>0.4639</v>
+        <v>-0.4639</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.1598</v>
+        <v>-1.3917</v>
       </c>
       <c r="R15" t="n">
-        <v>1.6237</v>
+        <v>0.9278</v>
       </c>
       <c r="S15" t="n">
-        <v>2.2699</v>
+        <v>0.5779</v>
       </c>
       <c r="T15" t="n">
-        <v>2.8115</v>
+        <v>0.6253</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.5416</v>
+        <v>-0.0474</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.6778999999999999</v>
+        <v>2.6495</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.6778999999999999</v>
+        <v>1.5773</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. JESSUP</t>
+          <t>N. GIFFEY</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.9259</v>
+        <v>2.1049</v>
       </c>
       <c r="E16" t="n">
-        <v>0.5006</v>
+        <v>1.5417</v>
       </c>
       <c r="F16" t="n">
-        <v>1.4253</v>
+        <v>0.5632</v>
       </c>
       <c r="G16" t="n">
-        <v>3.0396</v>
+        <v>1.5373</v>
       </c>
       <c r="H16" t="n">
-        <v>0.3963</v>
+        <v>0.3662</v>
       </c>
       <c r="I16" t="n">
-        <v>2.6433</v>
+        <v>1.1711</v>
       </c>
       <c r="J16" t="n">
-        <v>2.7934</v>
+        <v>1.6592</v>
       </c>
       <c r="K16" t="n">
-        <v>0.6722</v>
+        <v>0.6421</v>
       </c>
       <c r="L16" t="n">
-        <v>2.1212</v>
+        <v>1.0171</v>
       </c>
       <c r="M16" t="n">
-        <v>0.2462</v>
+        <v>-0.1219</v>
       </c>
       <c r="N16" t="n">
         <v>-0.2759</v>
       </c>
       <c r="O16" t="n">
-        <v>0.5221</v>
+        <v>0.154</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.4639</v>
+        <v>0.4639</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.3195</v>
+        <v>-1.1598</v>
       </c>
       <c r="R16" t="n">
-        <v>1.8556</v>
+        <v>1.6237</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.7221</v>
+        <v>0.7815</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.0455</v>
+        <v>1.0422</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.6765</v>
+        <v>-0.2607</v>
       </c>
       <c r="V16" t="n">
-        <v>1.0722</v>
+        <v>-0.6778999999999999</v>
       </c>
       <c r="W16" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-0.6778999999999999</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.4509</v>
+        <v>0.1281</v>
       </c>
       <c r="E17" t="n">
-        <v>-2.1135</v>
+        <v>-1.5237</v>
       </c>
       <c r="F17" t="n">
-        <v>1.6626</v>
+        <v>1.6519</v>
       </c>
       <c r="G17" t="n">
         <v>-0.9363</v>
@@ -1780,13 +1780,13 @@
         <v>1.6237</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.9063</v>
+        <v>-0.3273</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.0455</v>
+        <v>-0.4558</v>
       </c>
       <c r="U17" t="n">
-        <v>0.1393</v>
+        <v>0.1285</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>W. GABRIEL</t>
+          <t>J. HOLLATZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.7803</v>
+        <v>-2.444</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.5584</v>
+        <v>-1.8614</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.2219</v>
+        <v>-0.5826</v>
       </c>
       <c r="G18" t="n">
-        <v>2.1569</v>
+        <v>-2.1978</v>
       </c>
       <c r="H18" t="n">
-        <v>1.9795</v>
+        <v>0.2749</v>
       </c>
       <c r="I18" t="n">
-        <v>0.1774</v>
+        <v>-2.4727</v>
       </c>
       <c r="J18" t="n">
-        <v>2.4431</v>
+        <v>-1.3938</v>
       </c>
       <c r="K18" t="n">
-        <v>2.3695</v>
+        <v>0.3396</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0736</v>
+        <v>-1.7334</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.2862</v>
+        <v>-0.804</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.39</v>
+        <v>-0.06469999999999999</v>
       </c>
       <c r="O18" t="n">
-        <v>0.1038</v>
+        <v>-0.7393999999999999</v>
       </c>
       <c r="P18" t="n">
-        <v>-1.1598</v>
+        <v>0.6959</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.3195</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.1598</v>
+        <v>0.6959</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.8443000000000001</v>
+        <v>-0.4059</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.0351</v>
+        <v>-0.4676</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.8092</v>
+        <v>0.0617</v>
       </c>
       <c r="V18" t="n">
-        <v>-2.933</v>
+        <v>-0.5361</v>
       </c>
       <c r="W18" t="n">
-        <v>-0.6468</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-2.2862</v>
+        <v>-0.5361</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. HOLLATZ</t>
+          <t>W. GABRIEL</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-3.0559</v>
+        <v>-2.5</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.2153</v>
+        <v>-0.7943</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.8407</v>
+        <v>-1.7057</v>
       </c>
       <c r="G19" t="n">
-        <v>-2.1978</v>
+        <v>2.1569</v>
       </c>
       <c r="H19" t="n">
-        <v>0.2749</v>
+        <v>1.9795</v>
       </c>
       <c r="I19" t="n">
-        <v>-2.4727</v>
+        <v>0.1774</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.3938</v>
+        <v>2.4431</v>
       </c>
       <c r="K19" t="n">
-        <v>0.3396</v>
+        <v>2.3695</v>
       </c>
       <c r="L19" t="n">
-        <v>-1.7334</v>
+        <v>0.0736</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.804</v>
+        <v>-0.2862</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.06469999999999999</v>
+        <v>-0.39</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.7393999999999999</v>
+        <v>0.1038</v>
       </c>
       <c r="P19" t="n">
-        <v>0.6959</v>
+        <v>-1.1598</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-2.3195</v>
       </c>
       <c r="R19" t="n">
-        <v>0.6959</v>
+        <v>1.1598</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.0179</v>
+        <v>-0.5641</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.8215</v>
+        <v>-0.2711</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.1964</v>
+        <v>-0.293</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.5361</v>
+        <v>-2.933</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>-0.6468</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.5361</v>
+        <v>-2.2862</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-4.1301</v>
+        <v>-2.7997</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.1041</v>
+        <v>-0.5144</v>
       </c>
       <c r="F20" t="n">
-        <v>-3.026</v>
+        <v>-2.2853</v>
       </c>
       <c r="G20" t="n">
         <v>-2.7762</v>
@@ -2014,13 +2014,13 @@
         <v>0.9278</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.122</v>
+        <v>0.2084</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.4086</v>
+        <v>0.1812</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.7134</v>
+        <v>0.0272</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>I. MIKE</t>
+          <t>J. VOIGTMANN</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.2211</v>
+        <v>-4.7409</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.7034</v>
+        <v>-4.0252</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.5178</v>
+        <v>-0.7158</v>
       </c>
       <c r="G21" t="n">
-        <v>-4.3499</v>
+        <v>-4.1483</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.8501</v>
+        <v>-1.8463</v>
       </c>
       <c r="I21" t="n">
-        <v>-3.4999</v>
+        <v>-2.302</v>
       </c>
       <c r="J21" t="n">
-        <v>-3.0277</v>
+        <v>-2.4725</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.7423</v>
+        <v>-1.4887</v>
       </c>
       <c r="L21" t="n">
-        <v>-2.2854</v>
+        <v>-0.9838</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.3222</v>
+        <v>-1.6759</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.1078</v>
+        <v>-0.3577</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.2144</v>
+        <v>-1.3182</v>
       </c>
       <c r="P21" t="n">
-        <v>-1.6237</v>
+        <v>-0.6959</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.5515</v>
+        <v>-1.1598</v>
       </c>
       <c r="R21" t="n">
-        <v>0.9278</v>
+        <v>0.4639</v>
       </c>
       <c r="S21" t="n">
-        <v>1.8943</v>
+        <v>0.1032</v>
       </c>
       <c r="T21" t="n">
-        <v>1.8758</v>
+        <v>-0.393</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0185</v>
+        <v>0.4962</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.1418</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.1418</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>J. VOIGTMANN</t>
+          <t>I. MIKE</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-5.1513</v>
+        <v>-5.0518</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.379</v>
+        <v>-5.1188</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.7722</v>
+        <v>0.0669</v>
       </c>
       <c r="G22" t="n">
-        <v>-4.1483</v>
+        <v>-4.3499</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.8463</v>
+        <v>-0.8501</v>
       </c>
       <c r="I22" t="n">
-        <v>-2.302</v>
+        <v>-3.4999</v>
       </c>
       <c r="J22" t="n">
-        <v>-2.4725</v>
+        <v>-3.0277</v>
       </c>
       <c r="K22" t="n">
-        <v>-1.4887</v>
+        <v>-0.7423</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.9838</v>
+        <v>-2.2854</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.6759</v>
+        <v>-1.3222</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.3577</v>
+        <v>-0.1078</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.3182</v>
+        <v>-1.2144</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.6959</v>
+        <v>-1.6237</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.1598</v>
+        <v>-2.5515</v>
       </c>
       <c r="R22" t="n">
-        <v>0.4639</v>
+        <v>0.9278</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.3071</v>
+        <v>1.0635</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.7468</v>
+        <v>0.4604</v>
       </c>
       <c r="U22" t="n">
-        <v>0.4397</v>
+        <v>0.6032</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>-0.1418</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-6.8044</v>
+        <v>-5.1924</v>
       </c>
       <c r="E23" t="n">
-        <v>-6.9703</v>
+        <v>-6.1447</v>
       </c>
       <c r="F23" t="n">
-        <v>0.166</v>
+        <v>0.9523</v>
       </c>
       <c r="G23" t="n">
         <v>-5.8687</v>
@@ -2248,13 +2248,13 @@
         <v>1.8556</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.3996</v>
+        <v>0.2124</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.7073</v>
+        <v>0.1184</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.6923</v>
+        <v>0.094</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-7.4805</v>
+        <v>-5.5818</v>
       </c>
       <c r="E24" t="n">
-        <v>-4.6124</v>
+        <v>-3.4329</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.8681</v>
+        <v>-2.1489</v>
       </c>
       <c r="G24" t="n">
         <v>-4.6389</v>
@@ -2326,13 +2326,13 @@
         <v>0.6959</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.6096</v>
+        <v>0.2891</v>
       </c>
       <c r="T24" t="n">
-        <v>-1.3443</v>
+        <v>-0.1647</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.2653</v>
+        <v>0.4538</v>
       </c>
       <c r="V24" t="n">
         <v>-0.5361</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-24.8753</v>
+        <v>-20.157</v>
       </c>
       <c r="E25" t="n">
-        <v>-20.8475</v>
+        <v>-20.8474</v>
       </c>
       <c r="F25" t="n">
-        <v>-4.027800000000001</v>
+        <v>0.6902999999999988</v>
       </c>
       <c r="G25" t="n">
         <v>-18.0127</v>
@@ -2380,7 +2380,7 @@
         <v>-10.8462</v>
       </c>
       <c r="K25" t="n">
-        <v>0.1299999999999998</v>
+        <v>0.1300000000000002</v>
       </c>
       <c r="L25" t="n">
         <v>-10.9761</v>
@@ -2404,13 +2404,13 @@
         <v>12.7575</v>
       </c>
       <c r="S25" t="n">
-        <v>-3.4398</v>
+        <v>1.2782</v>
       </c>
       <c r="T25" t="n">
-        <v>0.2195999999999998</v>
+        <v>0.2195</v>
       </c>
       <c r="U25" t="n">
-        <v>-3.6592</v>
+        <v>1.0588</v>
       </c>
       <c r="V25" t="n">
         <v>-1.1032</v>
